--- a/data/prescription.xlsx
+++ b/data/prescription.xlsx
@@ -1,34 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22624"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Romens_Api_Test\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30915B5F-BE24-485A-9EB0-C0E6A0A975E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="getMedicationInter" sheetId="1" r:id="rId1"/>
-    <sheet name="getConfig" sheetId="2" r:id="rId2"/>
-    <sheet name="getDrugList" sheetId="3" r:id="rId3"/>
-    <sheet name="ordonUpload" sheetId="4" r:id="rId4"/>
-  </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
-</workbook>
+<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:workbookPr codeName="ThisWorkbook"/>
+  <s:bookViews>
+    <s:workbookView activeTab="9"/>
+  </s:bookViews>
+  <s:sheets>
+    <s:sheet name="getMedicationInter" sheetId="1" r:id="rId1"/>
+    <s:sheet name="getConfig" sheetId="2" r:id="rId2"/>
+    <s:sheet name="getDrugList" sheetId="3" r:id="rId3"/>
+    <s:sheet name="ordonUpload" sheetId="4" r:id="rId4"/>
+    <s:sheet name="getOnlineOrder" sheetId="5" r:id="rId5"/>
+    <s:sheet name="getPrescriptList" sheetId="6" r:id="rId6"/>
+    <s:sheet name="getHisPrescript" sheetId="7" r:id="rId7"/>
+    <s:sheet name="getShopLoginInfo" sheetId="8" r:id="rId8"/>
+    <s:sheet name="getAllShop" sheetId="9" r:id="rId9"/>
+    <s:sheet name="shopApply" sheetId="10" r:id="rId10"/>
+    <s:sheet name="saveShopLoginSignUrl" sheetId="11" r:id="rId11"/>
+    <s:sheet name="saveOrderSignUrl" sheetId="12" r:id="rId12"/>
+    <s:sheet name="saveOfflineSignUrl" sheetId="13" r:id="rId13"/>
+  </s:sheets>
+  <s:definedNames/>
+  <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
+</s:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="51">
   <si>
     <t>case_id</t>
   </si>
@@ -54,89 +52,160 @@
     <t>result</t>
   </si>
   <si>
+    <t>getMedicationInter</t>
+  </si>
+  <si>
+    <t>获取处方上传输入模板-查询成功</t>
+  </si>
+  <si>
     <t>post</t>
   </si>
   <si>
     <t>/Inquiry</t>
   </si>
   <si>
+    <t>{"QueryType": "getMedicationInter","Params": '{"speDrug":0,"key":"PRESCRIPTE_UPLOAD"}'}</t>
+  </si>
+  <si>
     <t>{"result": "0000", "msg": "获取成功"}</t>
   </si>
   <si>
     <t>通过</t>
   </si>
   <si>
-    <t>getMedicationInter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取处方上传输入模板-查询成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"QueryType": "getMedicationInter","Params": '{"speDrug":0,"key":"PRESCRIPTE_UPLOAD"}'}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>getConfig</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取配置-查询成功</t>
   </si>
   <si>
     <t>{"QueryType": "getConfig","Params": ''}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取配置-查询成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getDrugList</t>
   </si>
   <si>
     <t>搜索药品-查询成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getDrugList</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{"QueryType": "getDrugList","Params": '{"page":1,"keyword":"头孢","barcode":""}'}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ordonUpload</t>
   </si>
   <si>
     <t>上传处方-查询成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ordonUpload</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{"QueryType": "ordonUpload","Params": '{"DATA":[{"TEMPLATECODE":"MEMBER_INFO","UPDATE_FUNC":"","UPDATE_PARAMS":"","DATA_SERVER":[],"data":{"state":"0","values":{"NAME":"张三丰","SEX":"1","AGE":"35","TELPHONE":"","IDCARD":""}}},{"TEMPLATECODE":"PRESCRIPTE_UPLOAD","UPDATE_FUNC":"","UPDATE_PARAMS":"","DATA_SERVER":[],"data":{"state":"0","values":{"PERSCRIPT_CATE":"1","UP_PHONE":"13000000000"}}}],"goodsData":[{"COUNTS":"2","NUMBER":"1","UNITIDS":"粒","TIMES":"3","goodsprice":"","USAGE":"口服","DAYS":"1","goodsname":"头孢克洛胶囊","id":"0100029","spec":"0.25g6粒"},{"COUNTS":"1","NUMBER":"2","UNITIDS":"粒","TIMES":"3","goodsprice":"","USAGE":"口服","DAYS":"1","goodsname":"感冒康胶囊","id":"0100055","spec":"10粒2板"}],"ordImg":"http://doctor-1252032681.cos.ap-guangzhou.myqcloud.com/pharmacy_client/52be8928b33d41d0b1a487d0c55b0789.JPEG"}'}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getOnlineOrder</t>
+  </si>
+  <si>
+    <t>线上处方列表-查询成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getOnlineOrder","Params": '{"page":1}'}</t>
+  </si>
+  <si>
+    <t>getPrescriptList</t>
+  </si>
+  <si>
+    <t>获取今日外方处方单列表-查询成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getPrescriptList","Params": '{"orderCode":"","page":1,"status":""}'}</t>
+  </si>
+  <si>
+    <t>getHisPrescript</t>
+  </si>
+  <si>
+    <t>获取历史处方列表-查询成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getHisPrescript","Params": '{"date":"#yesterday#","orderCode":"","page":1,"status":""}'}</t>
+  </si>
+  <si>
+    <t>getShopLoginInfo</t>
+  </si>
+  <si>
+    <t>获取门店子账号信息-查询成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getShopLoginInfo","Params": ''}</t>
+  </si>
+  <si>
+    <t>getAllShop</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getAllShop","Params": '{"page":1,"keyword":""}'}</t>
+  </si>
+  <si>
+    <t>shopApply</t>
+  </si>
+  <si>
+    <t>申请调店-已经存在调店申请</t>
+  </si>
+  <si>
+    <t>{"QueryType": "shopApply","Params": '{"shopcode":"00000002@romens.cn","reason":"hjj"}'}</t>
+  </si>
+  <si>
+    <t>{"result": "0002", "msg": "已经存在调至 00000002@romens.cn 店的申请，请等待管理员审核"}</t>
+  </si>
+  <si>
+    <t>saveShopLoginSignUrl</t>
+  </si>
+  <si>
+    <t>保存门店子账号签名图片-查询成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "saveShopLoginSignUrl","Params": '{"signUrl":"http://doctor-1252032681.cos.ap-guangzhou.myqcloud.com/pharmacy_client/52be8928b33d41d0b1a487d0c55b0789.JPEG"}'}</t>
+  </si>
+  <si>
+    <t>saveOrderSignUrl</t>
+  </si>
+  <si>
+    <t>线上处方单调配、复合发药片-获取成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "saveOrderSignUrl","Params": '{"signUrl":"http://doctor-1252032681.cos.ap-guangzhou.myqcloud.com/pharmacy_client/52be8928b33d41d0b1a487d0c55b0789.JPEG","type":"1","guid":"#guid#"}'}</t>
+  </si>
+  <si>
+    <t>saveOfflineSignUrl</t>
+  </si>
+  <si>
+    <t>今日外方调配、复合发药片-获取成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "saveOfflineSignUrl","Params": '{"url":"http://doctor-1252032681.cos.ap-guangzhou.myqcloud.com/pharmacy_client/52be8928b33d41d0b1a487d0c55b0789.JPEG","type":"1","guid":"#guid#"}'}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -167,31 +236,23 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" borderId="0" fillId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" builtinId="0" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -457,17 +518,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="80.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+    <col width="17.875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="30.75" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="80.75" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -493,51 +558,278 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="10.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="73.75" customWidth="1" min="6" max="6"/>
+    <col width="84" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
       <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="20.625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="32.875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="153.125" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
       </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="16.25" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="37" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="169.625" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B35DC54-217A-49AA-8646-2B962EE74859}">
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="56.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="16.625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="37" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="166.625" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -563,50 +855,126 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="14.125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="18.375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="56.875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B42C75A9-BFAF-4640-AD55-831F85BDB51F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="71.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+    <col width="14.125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="18.375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="71.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,51 +1000,54 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD90FB2F-A7AA-4CC4-9F95-04290BFAB605}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="148.375" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="14.125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="18.375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="148.375" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -702,35 +1073,406 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
         <v>23</v>
       </c>
       <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="14.625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="48.25" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
       <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="17.875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="30.75" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="70.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
       </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="17.875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="30.75" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="80.75" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="16.75" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="28.75" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="41.75" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="10.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="21.375" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/data/prescription.xlsx
+++ b/data/prescription.xlsx
@@ -3,7 +3,7 @@
 <s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:workbookPr codeName="ThisWorkbook"/>
   <s:bookViews>
-    <s:workbookView activeTab="9"/>
+    <s:workbookView activeTab="11"/>
   </s:bookViews>
   <s:sheets>
     <s:sheet name="getMedicationInter" sheetId="1" r:id="rId1"/>
@@ -169,7 +169,7 @@
     <t>线上处方单调配、复合发药片-获取成功</t>
   </si>
   <si>
-    <t>{"QueryType": "saveOrderSignUrl","Params": '{"signUrl":"http://doctor-1252032681.cos.ap-guangzhou.myqcloud.com/pharmacy_client/52be8928b33d41d0b1a487d0c55b0789.JPEG","type":"1","guid":"#guid#"}'}</t>
+    <t>{"QueryType": "saveOrderSignUrl","Params": '{"signUrl":"http://doctor-1252032681.cos.ap-guangzhou.myqcloud.com/pharmacy_client/52be8928b33d41d0b1a487d0c55b0789.JPEG","type":"1","guid":"1160244e-2f15-11e8-af4123f5b1d"}'}</t>
   </si>
   <si>
     <t>saveOfflineSignUrl</t>
@@ -808,6 +808,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
